--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,6 +528,40 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des Sauvegardes</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Page d'administration pour déclencher, automatiser, et télécharger les sauvegardes de la base de données hospital.db avec rappel de stockage externe.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Tables backup_settings + backup_history dans db-service. Route /api/admin/backups. Permission manageBackups (admin). Flutter : BackupManagementScreen + BackupService Singleton.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,40 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Page Détail Incident (GMAO)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Remplacement du pop-up par une page complète affichant le cycle de vie, la cause racine, les pièces et l'historique de l'incident.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Backend enrichi (GET /api/issues/:id) avec équipement, audit trail et maintenance. Écran IssueDetailScreen avec 5 sections GMAO et timeline verticale. flutter analyze : 0 erreur. npm test : 32/32.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -596,6 +596,74 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hiérarchie GMAO : macro-catégories &amp; sous-catégories</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Ajout des tables equipment_macro_categories (Biomedical/Infrastructure/IT), equipment_subcategories (~626 entrées migrées), pm_protocols avec seed pour 8 types biomédicaux. Colonnes subcategory_id, macro_category_id, warranty_end_date, criticality sur equipment. Routes /api/categories et /api/pm-protocols. Modèles Flutter mis à jour (Equipment + PmProtocol). Filtrage IssueFormScreen basculé de category-text vers macroCategory.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32 tests Jest passent. flutter analyze --no-fatal-infos : 46 info préexistants, 0 erreur. Migration DB 100% idempotente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GMAO Phase 2 - Hiérarchie équipements &amp; protocoles PM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Refonte classification : macro-catégories (Biomedical/Infrastructure/IT), sous-catégories migrées depuis ~626 equipment_categories, table pm_protocols avec checklist JSON, champs criticality (A/B/C) et warranty_end_date sur equipment. CRUD backend + modèles Flutter mis à jour.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8 protocoles PM biomédicaux seedés. flutter analyze : 46 infos pré-existantes, 0 erreur. npm test : 32 passed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,36 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Amélioration EquipmentDetailScreen</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Refonte de la vue détail équipement : ajout criticité (A/B/C colorée), garantie avec badge d'état, macro-catégorie, sous-catégorie, et incidents cliquables naviguant vers IssueDetailScreen</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -694,6 +694,40 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
     </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Refonte écran login GMAO</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Séparation claire des 3 modes (connexion/inscription/reset), suppression du champ rôle à l'inscription, sécurisation des boutons DEV via kDebugMode, bannière d'alerte service, footer statut système, bouton 'Mot de passe oublié' proéminent, section comptes récents, 9 nouvelles clés i18n FR+EN.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Tous les flux i18n générés. flutter analyze --no-fatal-infos OK. Aucune régression détectée.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,40 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Login - layout responsive bureau/mobile</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Mise en page 2 colonnes sur bureau (≥800px, logo gauche, formulaire droit, pas de scroll global), layout mobile scroll sans comptes récents, statut système coin bas-droit, bouton langue affiche la langue courante (FR/EN).</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze --no-fatal-infos OK. Breakpoint 800px cohérent avec le reste de l'app.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -762,6 +762,40 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Redirection intelligente et Hub KPIs</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Redirection post-login basée sur le rôle (techniciens → IssueTracking direct). HomeHubScreen transformé en tableau de bord global GMAO avec 3 tuiles KPI dynamiques (incidents critiques/urgents, alertes stock, équipements hors service), FAB urgence 'Signaler un incident' et badges d'alerte sur les cartes modules.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Testé flutter analyze --no-fatal-infos. i18n FR+EN ajoutée (12 nouvelles clés). Visibilité RBAC des cartes modules respectée.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -796,6 +796,40 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Refonte Dashboard GMAO</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Refonte du tableau de bord : 5e StatCard PM en retard, tri incidents par urgence décroissante, alertes incidents critiques &gt;24h, indicateurs opérationnels technicien/superviseur, panel latéral desktop équipements critiques HS, indicateur de fraîcheur des données.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13 nouvelles clés i18n (FR+EN). Layout RBAC : vue simplifiée pour hospitalStaff, vue étendue pour techniciens/superviseurs/admins. 3e colonne desktop technicien. flutter analyze --no-fatal-infos OK.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -830,6 +830,40 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Refonte EquipmentListScreen</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Virtualisation SliverList, RBAC colonnes par rôle, formulaire Stepper 3 étapes, filtre PM, bouton Planifier PM, export CSV liste filtrée</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Correction bonus : clés ARB dashboard manquantes du commit précédent. flutter analyze --no-fatal-infos : EXIT 0.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -864,6 +864,240 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Refonte EquipmentDetailScreen</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Décomposition de l'écran monolithique (925 lignes) en 8 sous-widgets, navigation par onglets, vue RBAC hospitalStaff simplifiée, bannière critique, QR Code, MTTR, bouton PM, double confirmation suppression</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8 nouveaux fichiers dans lib/widgets/equipment/. ARB : 34 nouvelles clés FR+EN. flutter analyze --no-fatal-infos : 0 erreur/warning dans les nouveaux fichiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Refonte IssueFormScreen — UX &amp; GMAO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Garde-fou changement d'onglet, scanner QR biomédical, aperçu photo plein écran, switch disponibilité équipement, modale succès avec ticket ID et SLA par urgence.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>mobile_scanner ^6.0.0 ajouté. Sur web : fallback dialog saisie manuelle ID. SLA : Critique=2h, Urgent=12h, Moyen=48h, Faible=1sem. flutter gen-l10n régénéré.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Refonte IssueTrackingScreen GMAO</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Ajout recherche globale, filtres avancés (statut/urgence/période/groupe), tri urgence décroissante, vue Kanban desktop 4 colonnes, bouton Voir tout dans les encadrés personnels, et export CSV de la liste filtrée.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Kanban extrait dans lib/widgets/issues/kanban_board.dart. 24 clés ARB ajoutées (FR+EN). flutter analyze passe sans erreur (37 infos pré-existants).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Split View + Actions Superviseur IssueDetail</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Split View Gmail (&gt;=800px) dans IssueTrackingScreen : liste à gauche, IssueDetailScreen en panneau à droite. Bannière RBAC 'Pris en charge par', réassignation et commentaire pour supervisor/admin, timeline HH:mm, section Documents GMAO.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze --no-fatal-infos : 0 erreur. Fix value-&gt;initialValue DropdownButtonFormField. Clés i18n : issueDetailHandledBy, issueDetailReassign*, issueDetailComment*, issueDetailSectionDocuments, issueDetailPanelNoSelection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Espace Technicien Master-Detail &amp; Timer</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Layout split desktop (&gt;800px), chronomètre live d'intervention (Timer.periodic), sélecteur de pièces depuis inventaire, tooltip sur bouton résolu, agenda fixé sur takenAt</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Refonte ReportsScreen BI</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Ajout filtres temporels (7j/30j/90j/année/custom), KPIs GMAO (MTTR, conformité PM, top 3 depts), export CSV réel, i18n FR+EN</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>StatefulWidget + ListenableBuilder, calcul local sur DataService, export via csv_export.dart, widget ReportKpiSection extrait dans lib/widgets/reports/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Refonte AnalyticsScreen</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Suppression métriques IT (logins/failed logins), ajout graphiques fl_chart (LineChart tendances 13 semaines, BarChart par groupe technique), correction parsing equipment_by_status (Object→Map), croisement données issues/analytics</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Nouveaux widgets : lib/widgets/analytics/incident_trend_chart.dart, resolution_bar_chart.dart. 16 nouvelles clés i18n (FR+EN). fl_chart ^0.69.0 ajouté au pubspec.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1098,6 +1098,40 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Sécurisation BackupManagement</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Verrouillage strict rôle admin (RBAC guard dans build), masquage UI déjà assuré par requiredPermission, warning rouge si auto-backup désactivé, double confirmation par frappe RESTAURER avant restauration DB.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Garde UserRole.admin inviolable. Bouton Restaurer ajouté dans historique. BackupService.restoreBackup() ajouté. 14 nouvelles clés i18n FR+EN.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1132,6 +1132,138 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Audit et MAJ Dépendances</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Mise à jour sécurisée des packages Node.js et Flutter, résolution des alertes d'audit et vérification CI</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>auth-service: express 4.22.2, helmet 8.2.0, jwks-rsa 3.2.2. db-service: axios 1.16.1 (19 CVE résolus), express 4.22.2, helmet 8.2.0. flutter-app: cupertino_icons 1.0.9, shared_preferences 2.5.5. Risques résiduels documentés: tar (build-time/bcrypt) + xlsx (no-fix-available, admin-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Refonte LoginScreen et Access Request</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Remplacement du signup auto-declaratif par demande d'acces validee par admin, indicateur sante API discret (point colore + tooltip), contact urgence IT, banniere IAM actionnable.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Nouvel endpoint POST /api/auth/access-request, table access_requests en DB, kDebugMode verifie pour Quick Dev Login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Refonte HomeHubScreen par Rôle</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Transformation du hub en dashboard métier : vue actions rapides pour le personnel soignant, plan de travail GMAO pour les techniciens, KPIs + fraîcheur des données pour admins/superviseurs, FAB étendu.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>RBAC strict : hospitalStaff → gros bouton Signaler + incidents actifs ; technicien* → PM dues/en retard, interventions assignées, pièces en attente ; admin/superviseur → KPIs + indicateur lastRefresh + 3 modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Refonte DashboardScreen Adaptatif</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>StatCards interactives avec navigation filtrée vers EquipmentListScreen, responsive mobile corrigé (grille 2x2+1), vues par rôles (Météo de l'hôpital pour hospitalStaff, Mes tâches du jour pour techniciens) et auto-refresh Timer.periodic 5 min avec indicateur LinearProgressIndicator.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1264,6 +1264,74 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Refonte UX EquipmentListScreen</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Filtres persistants via EquipmentFilterState singleton, vue grille/liste desktop, colonnes adaptatives RBAC (Dernière PM pour techniciens), alertes PM inline sans filtre, export CSV mobile via share_plus, scan QR avec MobileScanner, droits édition étendus aux techniciens, filtre unité pour hospitalStaff.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7 fonctionnalités GMAO intégrées. share_plus 10.1.4. flutter analyze : 0 erreur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Refonte UX IssueFormScreen</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Formulaire en 2 étapes (catégorie+équipement+urgence / description+photos), urgence sélectionnable dès l'étape 1, mode équipement non répertorié (Bio+IT), guide visuel photos, bouton Scan &amp; Block QR urgence Critique.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Backend : hasEquipmentName ajouté pour autoriser equipment_name sans equipment_id. Scan &amp; Block saute directement à l'étape 2. i18n : 11 nouvelles clés FR+EN.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1332,6 +1332,40 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Refonte TechnicianUpdateScreen (Work Orders)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Badges d'onglets, chrono persistant (taken_at), déstockage transactionnel avec confirmation, workflow d'escalade (Waiting Materials/Redirected) et tri/groupement par département.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Backend: migration taken_at, PUT étendu (parts_consumed), PATCH /escalate. Flutter: groupement dept, dialog bon de travail (safety checkbox), dialog destock, dialog escalade.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1366,6 +1366,36 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dropdowns département/rôle dans demande d'accès</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Remplacement des champs texte libres département et rôle par des menus déroulants avec la liste des 18 départements de l'hôpital et des 7 rôles système dans le formulaire de demande d'accès.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1396,6 +1396,36 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Auto-inscription hospitalStaff sans validation admin</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Le formulaire 'Demander un accès' crée maintenant le compte Keycloak immédiatement avec le rôle hospitalStaff. Le dialog se ferme et l'utilisateur est auto-connecté sans intervention admin. Champs mot de passe ajoutés, dropdown rôle supprimé.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1426,6 +1426,40 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
     </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Préférences de Notifications Email</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Système permettant aux superviseurs, techniciens et admins de choisir quelles notifications email recevoir. Modal de 1ère connexion, section Settings, endpoints GET/PUT /api/users/me/notifications dans auth-service, table user_notification_preferences, service Brevo et endpoint interne pour db-service.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Backend: auth-service (DB migration + route notifications + email Brevo + endpoint interne /internal/notifications). Flutter: modèle NotificationPreferences, widget modal, section AccountSettingsScreen, détection 1ère connexion dans main.dart. i18n FR+EN.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1460,6 +1460,108 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Raccourci appel/email signaleur incident</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Boutons d'appel (tel:) et email (mailto:) dans la page détail d'un incident, sur la ligne du signaleur. reporter_phone ajouté en DB et transmis depuis le formulaire.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>url_launcher ^6.3.0 ajouté. Fonctionne web (mobile browser) et Android. Sur desktop, le tooltip affiche le numéro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Refonte Notifications — Incidents Critiques</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Remplacement des notifications génériques par des alertes ciblées sur les incidents CRITIQUES uniquement : technicien alerté à la création, superviseur alerté à la prise en charge, au diagnostic et à la résolution (avec KPIs : délai, diagnostic, actions, pièces). Suppression des notifications de changement de statut.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Backend: 4 nouvelles colonnes DB (notify_critical_*), 4 templates HTML Brevo avec KPIs. db-service: 3 déclencheurs dans PUT /api/issues (acknowledged, diagnosed, resolved). Flutter: modèle mis à jour, UI remaniée avec sections Technicien/Superviseur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Feature Flags et modularite</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Systeme d activation/desactivation des modules (equipment, inventory) par role, avec table feature_flags, endpoints auth-service et navigation dynamique Flutter</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Settings verrouille. Module Inventaire et Equipement desactivables globalement ou par role. 15 tests Jest. flutter analyze OK.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1562,6 +1562,142 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Scénarios de test RBAC par rôle</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Suite complète de tests manuels (Given-When-Then), Jest backend et flutter_test frontend couvrant les 7 rôles Keycloak et les 14 permissions applicatives</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Scénarios manuels dans tests/scenarios/, Jest dans auth-service/src/tests/ et db-service/src/tests/, widget tests dans flutter-app/test/rbac/ — constat de sécurité documenté : GET /api/inventory sans requireRole backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Tests widget Flutter RBAC</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Suite de tests flutter_test vérifiant la visibilité conditionnelle des éléments UI selon le rôle : hub screen routing, cartes modules, sidebar, dashboard et permissions AuthService</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Fichier : flutter-app/test/rbac/rbac_visibility_test.dart — 24 tests couvrant 7 groupes. flutter analyze --no-fatal-infos : exit code 0. flutter test bloqué par objective_c native hook (path avec espaces) — passer par CI Jenkins/Docker</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Scénarios de test RBAC par rôle — Bilan</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Clôture de la suite RBAC : note de synthèse, plan d'amélioration, 14/14 permissions couvertes, 176 nouveaux tests (73 Jest auth + 79 Jest db + 24 Flutter)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Lacune documentée : GET /api/inventory sans requireRole backend (ticket ouvert). Tests Flutter bloqués localement (objective_c path spaces), fonctionnels en CI Jenkins/Docker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Export PDF ReportsScreen</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Bouton téléchargement PDF sur ReportsScreen avec KPIs GMAO : équipements par statut/département/catégorie, incidents par urgence/statut/catégorie, PM en retard/imminentes, MTTR, inventaire critique. Génération côté client Flutter via PdfReportService (pdf + printing). Option B retenue.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Accessible aux utilisateurs ayant la permission generateReports (canGenerateReports). Bouton visible conditionnellement. Filtres V1 : période sélectionnée dans l'UI. Correction PdfColors.white70 → PdfColor(0.85,0.85,0.85). flutter analyze --no-fatal-infos : 0 erreur. objective_c native build failure est préexistant (mobile_scanner + local_auth).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1698,6 +1698,36 @@
         </is>
       </c>
     </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Ajustement UI statut équipement</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Réduction des marges et du padding du badge de statut dans EquipmentListScreen pour optimiser l'espace d'affichage.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1728,6 +1728,138 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Module Debug and Test</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Ajout d'un module d'administration pour réaliser des scénarios, incluant un endpoint et une page UI pour vider la table des incidents (issues).</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Backend: POST /api/debug/clear-issues (admin, audit trail). Frontend: DebugTestScreen avec dialog de confirmation + SnackBar + reloadIssues(). i18n FR/EN. flutter analyze: 0 erreur. npm test: 113 tests OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Téléchargement Rapports Historiques</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Ajout d'une section d'archivage sur ReportsScreen permettant de sélectionner et télécharger en PDF les rapports mensuels des 2 dernières années ainsi que les rapports annuels.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Optimisation UI Top Bar</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Réduction de l'encombrement vertical des onglets et sous-pages pour maximiser l'espace de données sur les écrans concernés.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>4 fichiers modifiés : issue_tracking_screen, technician_update_screen, equipment_detail_screen, settings_screen. Onglets icon+texte empilés (~72px) remplacés par onglets horizontaux Row compacts (40px). indicatorWeight réduit à 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Déplacement UI Validation</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Extraction de l'onglet 'À valider' depuis IssueTrackingScreen et intégration dans TechnicianUpdateScreen (onglet conditionnel canApproveRequests). Superviseurs accèdent désormais au module via alternativePermission.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>IssueTrackingScreen perd le TabController (plus simple). TechnicianUpdateScreen gagne 4 onglets pour admin/superviseur. main.dart: _NavItem.alternativePermission pour accès OR-permission.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1860,6 +1860,190 @@
         </is>
       </c>
     </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>PM - Checklist interactive</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Widget PmChecklistWidget avec cases à cocher RBAC, compteur de progression et fallback protocole absent. Modèle PmChecklistItem (fromJson multi-format string/map).</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze --no-fatal-infos : 0 erreur/warning. Accessible via GlobalKey depuis EquipmentMaintenanceTab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>PM - Fréquence de maintenance</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Dropdown fréquence dans onglet GMAO, UPSERT preventive_maintenance_plans via PUT /api/equipment/:id/pm-plan, audit trail. Fréquence persistée depuis pmPlan dans GET /api/equipment/:id.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>PM - Validation officielle</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>POST /maintenance enrichi : snapshot checklist, durée, pièces, calcul next_pm SQLite, déstockage inventaire. Migrations maintenance_records (5 nouvelles colonnes). Flutter : bouton RBAC, dialog confirmation, reload équipement.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>PM - Étiquette PDF</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>PdfLabelService Flutter (pdf+printing, A6 paysage, pattern PdfReportService). GET /api/equipment/:id/maintenance-label/:record_id backend (pdfkit). Bouton Imprimer dans dialog de validation + bouton autonome dans historique PM.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>PM - Notification J-7</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Job quotidien pm_reminder_job.js (24h interval, skip en NODE_ENV=test), appel POST /internal/notifications/send-to-roles auth-service type pm_due. Rappels J-7 et J=0 via SQLite date().</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>PM - Historique et conformité</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Section historique PM préventives dans onglet GMAO (filtre maintenance_type=preventive, 10 entrées + 'Voir tout'). KPI taux de conformité calculé côté Flutter (fenêtre fréquence+15j de grâce), badge coloré ≥80%/60-79%/&lt;60%.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2044,156 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
     </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Docs - Table equipment_documents + endpoints</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nouvelle table equipment_documents (3 types), multer upload, endpoints GET/POST/download/soft-delete, audit trail</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Docs - Table issue_photos + endpoints</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Table issue_photos, upload multipart max 5 photos, endpoint download par incident, audit trail</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Docs - Onglet Documents Flutter (2 sections + RBAC)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Widget EquipmentDocumentsTab complet, sections technique/intervention, upload file_picker, RBAC canManageEquipment, ApiClient.postMultipart</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Docs - Compression images IssueFormScreen</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>ImageCompressor service (web=bypass natif=placeholder), upload multipart photos après createIssue, max 5 photos</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Docs - Photos incidents dans IssueDetailScreen</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Section photos dans fiche incident, modèle IssuePhoto, grille vignettes 1-2 colonnes avec download et préview plein écran</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2194,6 +2194,40 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr"/>
     </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Corrections UX Mobile v3</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Responsivite TechnicianUpdateScreen (TabBar icones sur mobile &lt;600px), ReportsScreen (archives en tete, boutons responsifs), pagination EquipmentList en memoire (pageSize=20, reset sur filtre), titre sidebar dynamique par ScreenType, badge notifications sidebar desktop, vue lecture seule IssueStaffDetailScreen avec timeline horodatee pour hospitalStaff</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>6 taches UI Flutter - aucun changement backend ni schema DB - nouvel ecran issue_staff_detail_screen.dart cree (14 ecrans)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2228,6 +2228,40 @@
         </is>
       </c>
     </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Fix navigation KPI vers modules désactivés</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Les tuiles KPI du hub (alertes stock, équipements HS) ne naviguent plus vers des modules désactivés dans les settings. onTap mis à null si le module est inaccessible.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Fichier modifié : home_hub_screen.dart — _buildKpiRow et _KpiTile.onTap rendu nullable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2262,6 +2262,40 @@
         </is>
       </c>
     </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Boutons debug notifications</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Ajout de 2 endpoints backend (notify-now, notify-schedule) et 4 boutons Flutter dans DebugTestScreen pour tester l'envoi de notifications email depuis le panneau admin</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Type d'email utilise : critical_new_issue (auth-service). Scheduling in-memory uniquement — reinitialise au redemarrage du serveur. flutter analyze OK.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2296,6 +2296,36 @@
         </is>
       </c>
     </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Bannière push notifications</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Bandeau d'avertissement compact sur HomeHubScreen quand les notifications push ne sont pas activées. Bouton Activer déclenche requestAndSubscribe(), fermeture manuelle possible via X.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2326,6 +2326,40 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
     </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Masquage alertes dashboard selon feature flags</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Les alertes stock (out of stock, low level) du hub principal sont masquées quand le module Inventaire est désactivé dans les feature flags.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Correction dans home_hub_screen.dart _buildManagerView : stockAlertCount=0 si module inventory désactivé.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2360,6 +2360,40 @@
         </is>
       </c>
     </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>refactoring-clean-code-global</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Audit et refactoring Clean Code complet : centralisation TECH_ROLES/rolesCsv (5 routes → utils/roles.js), suppression dead code enrichEquipment, AppBreakpoints (18 occurrences), TabLabel widget, NavItem/ScreenType publics, AppSidebar/AppTopBar/AppBottomNav extraits de main.dart, _AvailableIssueCard + helpers top-level depuis TechnicianUpdateScreen</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze 0 error 0 warning. npm test 113/113. main.dart réduit de 991 à 436 lignes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2394,6 +2394,40 @@
         </is>
       </c>
     </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Correctif et OS Notifications</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Ajout cloche HomeHub avec badge, fix flux DebugTestScreen vers notifs in-app, table notifications DB, endpoints GET/PATCH /api/notifications, fetchFromApi dans NotificationService, OsNotificationService stub, i18n 7 clés</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Table notifications créée dans hospital.db via migration idempotente. Cloche visible dans HomeHubScreen._buildHeader. DebugTestScreen appelle fetchFromApi après notify-now. Endpoints ajoutés dans push_notifications.js sur /api/notifications existant.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2428,6 +2428,36 @@
         </is>
       </c>
     </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Refonte UI Administration</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Refonte du SettingsScreen : 4 onglets NavigationRail (Départements CRUD API-backed + stats, Catégories arborescence macro/sub, Rôles &amp; Permissions + Ordre menu fusionnés, Journal d'activité paginé). Backend : routes CRUD /api/departments + POST/PUT/DELETE /api/categories/sub. Seed 18 départements hôpital.</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2458,6 +2458,36 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
     </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Role Detail Screen &amp; Hiérarchie</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Page de configuration dédiée par rôle (4 onglets : hiérarchie parent/enfant, permissions, ordre menu sidebar, utilisateurs). Table role_hierarchy SQLite + 3 endpoints GET backend. Navigation depuis l'onglet Rôles des Paramètres.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2488,6 +2488,74 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
     </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Audit KPI application v3</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Audit complet backend+Flutter+sécurité+docs via skill audit-gmao-kpi, score 83,5/100, rapport audit/rapport_audit_2026-06-10.md</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 correctifs priorisés inclus. context.md et CLAUDE.md mis à jour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Sécurisation access-request</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Correctif #1 audit : rate-limiter 3/h/IP sur POST /api/auth/access-request, compte créé avec VERIFY_EMAIL obligatoire avant connexion, audit trail sendLog</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>166/166 tests auth-service (dont 6 nouveaux + isolation test /health). context.md et CLAUDE.md mis à jour.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2556,6 +2556,40 @@
         </is>
       </c>
     </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Plan de remplacement biomédical</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Durée de vie de référence par sous-catégorie + calcul serveur statut/horizon + écran gestion sous-catégories + page détail + badges triangle + section notifications + rapport PDF plan de remplacement (RA3 S5)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Endpoints GET /api/equipment/replacement-plan (admin/supervisor), PUT /api/categories/sub/:id/lifespan (admin). 19 tests calcul. flutter analyze sans erreur.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2590,6 +2590,36 @@
         </is>
       </c>
     </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Catalogue Fabricant/Modèle + Catégories sous Équipements</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Onglet Catégories déplacé dans le menu Équipements ; nouvelles tables equipment_brands/equipment_models/model_documents/model_pm_protocols auto-seedées, endpoints CRUD, écrans détail fabricant et modèle (fiche = documents + protocoles PM).</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2620,6 +2620,70 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
     </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Masquage tuiles KPI modules désactivés</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Les tuiles KPI du hub (incidents/hors-service/stock) sont retirées quand leur module est désactivé via feature flags ; rangée recomposée, masquée si vide, tuile unique alignée à gauche en mobile.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Réforme &amp; cycle de vie équipements</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Soft delete (décommissionnement statut Disposed enrichi : motif, méthode, remplaçant) + garde-fou hard delete (409 si historique, force admin) ; workflow proposition→validation</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>DB +7 colonnes idempotentes ; endpoints propose-disposal/decommission ; DELETE garde-fou ; GET exclut Disposed (include_disposed); UI dialog réforme responsive + liens bidirectionnels + filtre liste. 16 tests verts, analyze 0 erreur.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2684,6 +2684,36 @@
         </is>
       </c>
     </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Rapport d'intervention par incident</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Rapport structure editable 1:1 par incident (resume, cause racine, recommandations, duree, cout, etat final, signatures), fige a la cloture, export PDF + archivage auto dans l'historique equipement, branche MTTR/cout</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2714,6 +2714,40 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
     </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Métadonnées cliquables fiche équipement</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Drill-down depuis la fiche équipement vers sous-catégorie/fabricant/modèle/catégorie/département + breadcrumb cliquable sur toutes les fiches de détail (vue complète)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Backend lecture seule (BASE_SELECT enrichi brand_id/brand_name, GET /api/categories/detail, GET /api/departments/:id/detail). 2 nouveaux écrans Flutter. 6 tests Jest.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2748,6 +2748,70 @@
         </is>
       </c>
     </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Déploiement IP-only par défaut</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Bascule du chemin de déploiement par défaut sur IP publique brute + certificat auto-signé ; retrait des références codées en dur à kabutare.duckdns.org (config.js, CLAUDE.md, contexte.md, plan.md, fixtures). Famille domaine conservée mais débranchée.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>config.js BREVO_SENDER_EMAIL -&gt; noreply@hospital.local ; plan.md réécrit autour de setup_ubuntu.sh ; limitation SPF/DKIM documentée. npm test auth-service: 166/166 OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Incidents par département + téléchargement rapport finalisé</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Page détail département : KPI incidents ouverts, sections en cours/résolus avec badge catégorie + cible (équipement/lieu) cliquables ; dialogue de téléchargement du PDF à la finalisation du rapport d'intervention</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2812,6 +2812,66 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
     </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Alertes urgentes cliquables + prise en charge rapide</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Drill-down des AlertCard dashboard + banniere critique vers onglet Incidents + bouton Prendre en charge technicien sur incidents prioritaires</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Refonte page technicien</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Onglet A valider en premier, planning en page separee, validation+reassignation deleguees au detail d'incident (bouton Examiner), delai de signalement affiche</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2872,6 +2872,70 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
     </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Suivi incidents 3 onglets</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Refonte IssueTrackingScreen en 3 onglets (Mes signalements / Tous actifs / Terminés), suppression split view, clic ouvre la page détail, colonne resolved_at backend</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Flutter + db-service. Tabs avec badges compteurs, date de résolution sur onglet Terminés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Ré-agencement cartes page Rapports</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Appairage Breakdown by status + Issue statistics, et Equipment by department + Equipment by category, dans les deux LayoutBuilder de ReportsScreen (responsive conservé).</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2936,6 +2936,40 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
     </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Refonte fiche équipement (4 onglets)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Onglet Info: édition par champ inline, description sous-cat, résumé d'état, notifications cliquables (durée de vie/incident/PM/remplacement), QR+étiquette PM. Maintenance: section PM réagencée, historique cliquable + étiquette d'époque. Notifications retirées des autres onglets.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Nouvelle colonne equipment_subcategories.description (migration idempotente).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2970,6 +2970,224 @@
         </is>
       </c>
     </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Audit volume flux de connexion</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Audit lecture seule du volume de donnees (bundle web + payloads API du login) du premier acces sur dev.app.lucaslopvet.fr, profils admin et hospitalStaff, recommandations bas-debit chiffrees</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Lecture seule, aucune modif de code</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Correction badge statut + retrait modif inline liste equipements</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Fix overflow visuel StatusBadge (ellipsis + tooltip) et suppression des 3 boutons Modifier redondants dans l'onglet Liste equipements (modification conservee uniquement sur la fiche detail)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Alerte sous-catégorie vide + actions déplacées vers fiche détail</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Icône d'alerte si equipment_count=0 dans la liste des sous-catégories ; Modifier/Supprimer une sous-catégorie déplacés de l'onglet Catégories vers subcategory_detail_screen.dart (pattern brand_detail_screen)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Localisation incident + filtres scrollables</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Champs Bâtiment/Lieu précis ajoutés aux onglets Bio/IT/Autre du formulaire d'incident ; bloc filtres de la page de suivi rendu scrollable avec la liste (NestedScrollView)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Popup sélection de rôle post-création de compte</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Renommage 'Demander un accès' -&gt; 'Créer un compte' ; popup obligatoire de sélection de rôle (technicien/superviseur/garder hospitalStaff) affiché une fois après création de compte, réutilisable depuis Paramètres</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Suppression blocage email non vérifié</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Retrait de requiredActions VERIFY_EMAIL à la création de compte (register + access-request) ; script one-shot de déblocage des comptes existants</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Bannières informatives conservées, emailVerified reste false, aucun changement Flutter</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Reset BDD démo (page Debug) + fix bug --dry-run imports</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Bouton admin Réinitialiser la base de données (équipements/incidents/inventaire/lieux) dans le module Debug, appelant POST /api/debug/reseed (seed.js refactorisé en fonction exportable). Corrige aussi le bug de config.js qui rendait --dry-run inopérant sur import_inventory.js et import_infra_inventory.js (lecture tardive de process.env.DB_PATH).</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3188,6 +3188,100 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
     </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Validation rapide incident + statut Rejected + détachement</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Sheet responsive de validation (signaleur, objet, photos, antécédents) avec valider/rejeter(motif)/réassigner groupe ; statut Rejected ; PATCH /reject &amp; /detach ; détachement technicien retour au pool</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Testé Chrome + Android. Réassignation = groupe uniquement. Pas de migration DB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Page Paramètres application (Settings)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Onglets Feature Flags + Paramètres généraux ; table app_settings (contact login public + config Brevo base/env, clé masquée) ; email de test ; suppression de l'écran feature flags autonome</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Régénération BDD depuis fichier XLSX (page Debug)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Bouton admin upload .xlsx (format Equipment Migration Template) qui vide équipements/incidents puis réimporte intégralement via POST /api/debug/reseed-from-file, en réutilisant seedReferences/importEquipment de import_inventory.js. Complète le bouton de reset démo existant.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3282,6 +3282,66 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
     </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Téléphone optionnel à la création de compte</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Champ téléphone optionnel ajouté au formulaire Demande d'accès, propagé à Keycloak et tracé dans access_requests.phone</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Correctifs parcours hospitalStaff</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Fix departement vide signalement non repertorie, navigation My active incidents -&gt; Issue Tracking, filtre+compteur incidents par departement, masquage rapport intervention/export CSV pour hospitalStaff</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3342,6 +3342,36 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
     </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Carte incident disponible cliquable</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Clic sur la carte de l'onglet Disponibles (page technicien) ouvre IssueDetailScreen en consultation, sans impacter les boutons Prendre en charge / Feuille de details</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3372,6 +3372,70 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
     </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Fix refresh technicien + photos incident perdues</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Polling 5min sur IssueTrackingScreen + gestion erreur Multer + visibilite echec upload photo + vraie compression image (cause racine)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Cause racine confirmee par lecture de code : ImageCompressor.compress() etait un placeholder no-op (web ET natif), renvoyant les bytes originaux sans jamais compresser. Une photo de smartphone (souvent 3-12 Mo) depassait donc systematiquement la limite serveur MAX_PHOTO_MB=5 (db-service/src/middleware/upload.js), Multer rejetait le fichier, et l'erreur etait avalee silencieusement cote Flutter (catch vide) + cote serveur renvoyait une page HTML 500 brute (pas de middleware d'erreur Express). Corrige : implementation reelle de la compression via package:image (deja present en transitif, pur Dart, fonctionne web+natif), ajout du middleware d'erreur Multer global, et affichage explicite + bouton Reessayer dans le dialogue de succes si l'upload photo echoue malgre tout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Liaison tardive équipement-incident</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /api/issues/:id/link-equipment + UI technicien pour rattacher un équipement à un incident créé sans équipement, avec horodatage equipment_linked_at</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3436,6 +3436,36 @@
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
     </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Page dédiée mise à jour intervention technicien</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Liste cliquable ouvrant une page séparée (plus de master-detail latéral) ; masquage réactif du sélecteur de pièces si module Inventaire désactivé ; garde-fou anti-perte de saisie</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3466,6 +3466,36 @@
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr"/>
     </row>
+    <row r="94" ht="28" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Rapport intervention auto à la clôture</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Génération et finalisation automatique du rapport d'intervention (table issue_intervention_reports) à la clôture du Bon de Travail technicien, mapping depuis diagnostic/actions/chronomètre, PDF archivé sur l'équipement si applicable</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3496,6 +3496,104 @@
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
     </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Visibilité admin demandes de rôle</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Notification cloche + section dédiée dans l'écran Users pour les role_change_requests en attente, mirroir du pattern department_change_requests, avec badge d'ancienneté</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Boucles d'intervention multi-passages</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Table issue_intervention_sessions 1:N, rapport PDF par boucle, suivi cliquable sur fiche incident technicien</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>3 routes backend + 13 tests Jest, modele Flutter IssueInterventionSession, widget InterventionSessionsTimeline, PDF PdfReportService.generateInterventionSessionReport</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Simplification — boucles intervention</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Refactor qualité : helper _s() PDF promu statique, appendLine dans issues.js, hasRole() dans utils/roles.js, _buttonSpinner() Flutter, note TODO sur _notifyUser.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>5 fixes simplification/réutilisation. flutter analyze --no-fatal-infos passe (105 info pré-existants, 0 error/warning).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3594,6 +3594,36 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Formulaire équipement enrichi</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Dropdowns brand/model en cascade avec création inline, tag physique (equipment_tags), champ building, toggle PM avec pré-remplissage fréquence depuis le protocole du modèle sélectionné</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3624,6 +3624,40 @@
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
     </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Seed db-service avec inventaire réel 2025-2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Remplacement de seed.js (db-service) par des données réelles : 338 équipements (tags réels) issus de l'inventaire physique XLSX, 173 enregistrements de maintenance issus du plan PPM Q1+Q2, issues ré-ancrées sur de vrais équipements</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Fichier combiné inventaire (Maternity/Neonatology/Pharmacy etc.) écarté : structure corrompue/incohérente (colonnes décalées en fin de fichier), non hardcodé. locations[] et inventory[] consommables conservés inchangés, aucun des 3 fichiers source ne couvrant ces 2 tables. npm test : 223/223 OK.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3658,6 +3658,36 @@
         </is>
       </c>
     </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Validation incidents par techniciens</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Permission approveRequests étendue aux 4 rôles technicien (Reported→Acknowledged), sans filtre groupe ni criticité</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3688,6 +3688,36 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
     </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Fusion Save / Save-and-Close</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Un seul bouton ElevatedButton ferme toujours la session active ; toggle conditionnel _planNextAction pour next_actions optionnel sans validation minimum</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3718,6 +3718,104 @@
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
     </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Option Autre catégorie Infrastructure</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Ajout option Autre dans le dropdown catégorie du Tab Infrastructure pour permettre de signaler un incident hors catalogue, masquage des dropdowns sous-catégorie et problème spécifique</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Fix onglet À valider techniciens</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>_openIssuesForValidation incluait uniquement admin/supervisor ; ajout du filtre par groupe (Biomédical/IT/Infrastructure) pour les techniciens disposant de la permission approveRequests</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>technician_update_screen.dart:124-141</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Intégration inventaire combiné (lits/mobilier) dans seed.js</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Ajout des 542 actifs supplémentaires (hors doublons) issus de 'INVENTORY combined october.xlsx' au seed db-service, avec parsing robuste par classification de cellule (colonnes décalées à partir de la section Pharmacie). Total equipment[] : 880 (338 biomédical + 542 mobilier/divers). Maintenance records enrichis à 188 grâce aux nouveaux noms d'équipement disponibles pour le matching PPM.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Correctif d'un bug de parsing initial (colonne NO confondue avec QTY, faussant serial_number) détecté et corrigé avant intégration finale. npm test : 223/223 OK.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3816,6 +3816,70 @@
         </is>
       </c>
     </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Fix fermeture session intervention</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Save and close créait/mettait à jour la session active via PUT sessions/active avant le POST sessions/active/close, évitant l'erreur 400 'Aucune session active' quand la dialog Compléter le diagnostic n'avait jamais été ouverte</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>technician_intervention_update_screen.dart _doSaveAndClose</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Documents PDF d'intervention</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Visualisation PDF a la cloture, upload complementaire multi-fichiers, remplacement du rapport d'intervention manuel par la liste des documents reels, badge + KPI taux de cloture documentee</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3880,6 +3880,66 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
     </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-106</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Bouton Actualiser + pagination serveur</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Pagination serveur (page/limit/search) sur GET /api/equipment et GET /api/issues, bouton Actualiser sur Équipements/Suivi incidents/Interventions technicien, cache DataService global inchangé</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-107</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Réduction flux premier accès</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Compression nginx JS/WASM + cache immutable assets, middleware compression API, payload light equipment, fusion 6 requêtes sidebar, cache conditionnel If-None-Match/304 — premier accès ~11 Mo → ~3,6 Mo (estimé, code prêt mais non déployé)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3940,6 +3940,36 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
     </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-108</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Verrouillage mode Debug &amp; Test</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Mot de passe admin defini au deploiement (setup_ubuntu.sh, partage prod/dev via /etc/kabutare/.env), requis en plus de Permission.manageFeatures pour afficher l'item sidebar Debug &amp; Test</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3970,6 +3970,40 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
     </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Réorganisation Roles &amp; Permissions + page Admin</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Déplacement Page Access by Role dans le détail de rôle (trié par module), suppression Menu Order dupliqué et onglet Activity Log redondant, en-tête page Admin repliable au scroll</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Aucun changement backend ; corrige au passage la non-persistance des checkboxes de permission de l'ancienne section Page Access</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4004,6 +4004,70 @@
         </is>
       </c>
     </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-110</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Filtrage timeline incident photos</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Exclusion des actions techniques upload_issue_photos/download_issue_photo de la timeline d'audit d'un incident (GET /api/issues/:id), sans impact sur l'audit trail global</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Modification SQL uniquement, db-service/src/routes/issues.js lignes 212-218</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-111</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Rapports PDF GMAO en anglais + letterhead + numéro de référence</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Traduction complète des 4 générateurs PDF (pdf_report_service.dart) en anglais fixe, ajout logo + adresse officielle (Southern Province / Huye District / Kabutare District Hospital / P.O. Box 621 Butare / Email), ajout numéro de référence unique par rapport</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4068,6 +4068,126 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
     </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-112</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Seuil urgence notification technicien</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Sélecteur de niveau d'urgence minimal (Faible/Moyen/Urgent/Critique) à côté du switch email 'nouvel incident' dans les préférences de notification technicien</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-113</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Fix Mark Resolved sans session active</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Corrige _doWorkOrderClose : appelle saveActiveInterventionSession avant closeActiveInterventionSession pour garantir qu'une session est créée et que diagnosis/action_taken/outcome sont persistés, même si aucune session n'existait préalablement.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-114</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Rapport intervention PDF : header/footer + regroupement documents</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Retrait Parts Replaced du PDF final, n° incident en pied de page (INC-xxx sur chaque page), documents d'intervention groupés par incident avec ExpansionTile sur la fiche équipement</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-115</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Clôture intervention → Disposed</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Bouton irréparable dans TechnicianInterventionUpdateScreen : PATCH /issues/:id/close-as-disposed, issue Completed + équipement Disposed en transaction</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4188,6 +4188,66 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
     </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-116</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Enrichissement fiche incident</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Affichage localisation complète (location_text/tag), indicateur téléphone absent, section 3 incidents récents liés à l'équipement avec lien fiche équipement</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-117</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Fix nav hub technicien mobile</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Ajout bouton CTA permanent + badge dans le hub technicien pour accéder à TechnicianUpdateScreen depuis le hub mobile. Refactoring _buildPmTile/_buildIssueTile avec onTap paramètre.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4248,6 +4248,36 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
     </row>
+    <row r="119" ht="28" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-118</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Onglet Documents interventions (page technicien)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Liste/filtre par technicien et periode des documents d'intervention cross-equipement, export ZIP et impression PDF fusionnee, nouvelle permission viewInterventionDocuments</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4278,6 +4278,36 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
     </row>
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-119</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Guide installation PWA iOS pour notifications</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Détection iOS/standalone/support Push/permission refusée, guidant l'ajout à l'écran d'accueil requis par Safari pour les notifications push app fermée</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4308,6 +4308,36 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
     </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-120</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Case document inline + rapport final équipement</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Case a cocher inline remplace le dialog post-hoc d'ajout de document ; generation auto d'un rapport final equipement (resume interventions + KPI MTTR/reouverture/downtime) a chaque Mark Resolved</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4338,6 +4338,36 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
     </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-121</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Filtre type document intervention</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Cases a cocher (rapport d'intervention / rapport de fin d'intervention) pour filtrer liste + export ZIP/PDF de l'onglet Documents technicien</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4368,6 +4368,134 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
     </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-122</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Navigation demande de rôle vers détail utilisateur</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Ligne de demande de rôle cliquable vers UserDetailScreen ; validation/rejet possible depuis l'écran de détail (même logique que les demandes de département)</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-123</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Badge validation + scission par groupe technicien</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Badge rouge sidebar (compteur incidents a valider par groupe) et separation de l'onglet A valider en 2 listes (mon groupe validable / autres techniciens lecture seule)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-124</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Détails intervention + documents dans onglet Incidents</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Panneau dépliable par incident (diagnostic, actions, durée, coût, documents PDF) dans l'onglet Incidents de la fiche équipement, sans changement backend</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze OK (0 erreur). Test manuel navigateur non effectué (Keycloak/auth-service indisponibles en local, décision utilisateur de skip). Refactor /simplify : carte incident extraite en StatefulWidget dédié (état d'expansion local par carte au lieu d'un Set au niveau de l'onglet), formatage coût aligné sur le format existant (toStringAsFixed(0) + RWF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-125</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Fiche détail incident + rejet technicien</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Navigation carte 'À valider' vers la fiche détail incident avec bandeau Valider/Rejeter, correctif RBAC permettant aux techniciens de rejeter, document PDF de rejet archivé sur l'équipement</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze 0 erreur, npm test db-service 281/281 passés. Vérification manuelle non effectuée (stack Keycloak indisponible dans cet environnement).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4496,6 +4496,36 @@
         </is>
       </c>
     </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-126</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Annexes rapport intervention + rapport final par incident</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Section annexes indexée (documents/photos) sur le rapport d'intervention ; nouveau rapport final par incident (KPI + résumé) généré systématiquement au Mark Resolved, y compris sans équipement lié</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4526,6 +4526,66 @@
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
     </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-127</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Fermeture auto fiche incident après validation</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>IssueDetailScreen se ferme automatiquement après Valider/Rejeter réussi (Navigator.pop), alignée sur le pattern equipment_detail_screen.dart:583-587</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-128</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Regroupement par issue + export PDF fusionné (onglet Documents technicien)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Documents d'intervention groupés par issue (ExpansionTile, tri par date d'incident) sur l'onglet technicien cross-équipement, avec bouton de fusion PDF par groupe (endpoint /print-pdf étendu avec issue_id).</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4586,6 +4586,40 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
     </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-129</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Sous-groupes Intervention/Annexe + tampon PDF + sommaire</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Onglet Documents technicien : sous-sections Intervention/Annexe par incident, tampon PDF permanent (annexe N, incident, page) sur pièces jointes et photos dès l'upload, sommaire conditionnel et réordonnancement du merge PDF par incident (rapport final -&gt; sommaire -&gt; intervention -&gt; annexes).</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Backend : 296 tests db-service passent (dont annex_stamp_service.test.js, intervention_documents.test.js). Flutter : flutter analyze --no-fatal-infos 0 erreur. Vérification navigateur non effectuée (stack Keycloak/Docker indisponible dans cet environnement).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4620,6 +4620,36 @@
         </is>
       </c>
     </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-130</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Cases à cocher export documents technicien</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>3 cases (Intervention/Piece jointe/Photo) pilotant liste + exports ZIP/PDF (global et par incident), rapport final toujours inclus, onglet scrollable mobile</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4650,6 +4650,74 @@
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
     </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-131</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Rétention des sauvegardes 7j+1/mois</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Rotation automatique des backups (backup.sh + système in-app) : 7 derniers jours conservés intégralement, puis 1 backup par mois calendaire au-delà</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Fenêtre fixe dans le code, pas de config UI. Rotation appelée après chaque backup manuel/auto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-132</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Icône PWA écran d'accueil</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Régénération icônes maskable/apple-touch avec safe-zone, correction start_url/scope manifest pour /app_isis/, logo hôpital visible sur Android et iOS au lieu du fallback monogramme</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostic confirmé par inspection (icônes maskable identiques aux normales sans safe-zone + transparence + start_url/scope absolus). Vérifié via serveur statique reproduisant /app_isis/ (fetch manifest+icônes 200, dims correctes, crop circulaire OK). Build flutter complet et Lighthouse impossibles dans cet environnement (bug pré-existant Flutter Windows : hook native assets objective_c échoue sur chemin contenant des espaces, indépendant de cette tâche). Test sur appareils réels Android/iOS non réalisé (aucun device disponible dans cette session) — a valider manuellement après déploiement. Effet de bord mineur documenté : le nouveau fond blanc opaque de Icon-192.png crée un contraste très léger (quasi imperceptible, #FFFFFF vs #F9FAFB) sur l'écran de chargement k-loading, non corrigé (bloc non modifié comme demandé sauf nécessité avérée).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4718,6 +4718,108 @@
         </is>
       </c>
     </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-133</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Onglets page détail incident</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Réorganisation de IssueDetailScreen en 4 onglets (Identification/Intervention/Documents/Historique), onglet Documents masqué pour hospitalStaff</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze OK (0 erreur sur le fichier). Test manuel navigateur non effectué (stack Keycloak+backend indisponible en sandbox) - à valider manuellement avant mise en prod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-134</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Fix boutons rognés étape 2 signalement mobile</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Row 3 boutons Retour/Annuler/Envoyer remplacée par Column 2 lignes (Retour+Annuler / Envoyer pleine largeur) + hauteur tactile min 48dp, corrige le rognage du bouton Annuler sur téléphone</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze OK (0 erreur sur le fichier). Vérification navigateur impossible dans cet environnement (bug preexistant: chemin avec espaces casse le hook de build native assets objective_c pour flutter run).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-135</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>PWA installable + CA interne + page offline</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>CA interne 2 étages avec page /setup/ guidée (Android/iOS/PC + QR), page offline anglaise via SW, fusion SW dans build_and_push.sh, mise à jour silencieuse vérifiée</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Renouvellement cert sans action téléphone ; saisie offline volontairement hors scope ; SW Flutter 3.41 = stub sans cache, précache offline.html assuré par push_sw.js</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4820,6 +4820,40 @@
         </is>
       </c>
     </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-136</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Suppression bouton Mettre a jour l'incident</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Retrait du bouton redondant en bas de la page detail incident (IssueDetailScreen) qui dupliquait l'onglet Intervention ; nettoyage du callback onNavigate devenu mort et de la cle i18n associee.</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze --no-fatal-infos OK sur issue_detail_screen.dart et issue_tracking_screen.dart</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4854,6 +4854,40 @@
         </is>
       </c>
     </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-137</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Refonte Documents/Intervention fiche incident</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Permission gating onglet Documents, archivage PDF dernière boucle, résumé Follow up basé sur les boucles, sous-catégorie Annexe (pièces jointes + photos) sur incident et équipement</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Ajout colonne next_action_due_at ; correctif bonus splitInterventionAnnexe (photos manquantes sur onglet Documents technicien existant)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4888,6 +4888,40 @@
         </is>
       </c>
     </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-138</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Corrections documents fiche incident</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Fix glyphe cassé PDF (tiret cadratin), renommage anglais des fichiers PDF archivés, correction/surfaçage de la disparition de pièces jointes photo à la clôture Bon de Travail, audit trail des échecs de tamponnage</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Cause confirmee par inspection de code : catch(_) muet dans _uploadPickedDocumentsIfAny avalait silencieusement tout echec de POST /documents (reseau, timeout, 401 non rafraichissable, 500) sans jamais avertir le technicien ni tracer l'echec cote serveur - corrige en surfacant le resultat (retour bool + SnackBar + logAction annex_stamp_failed). Piste JPEG progressif explicitement ecartee (revertDocumentAnnexStamp garde le document en base, juste sans annex_number) mais en ecrivant le test de non-regression demande, un VRAI bug a ete trouve et corrige dans annex_stamp_service.js : JpegEmbedder de pdf-lib lit imageData.buffer sans respecter byteOffset/byteLength, ce qui casse sur tout buffer issu du pool interne de Node (fichiers &lt; 4 Ko lus via fs.readFileSync) meme si le JPEG source est valide - corrige par une recopie defensive dans un buffer non poole avant embedJpg/embedPng, avec test de regression dedie. Piste ordre des operations (upload apres plusieurs awaits non catches dans _doWorkOrderClose) confirmee comme risque residuel documente, non modifiee (hors perimetre du prompt). Verification : npm test db-service 315/315 OK, flutter analyze 0 erreur. Docker indisponible dans cet environnement -&gt; scenarios manuels UI non rejoues en direct, valides par inspection de code + tests automatises cibles.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4922,6 +4922,40 @@
         </is>
       </c>
     </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-139</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Correctifs documents intervention &amp; fusion PDF</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Reordonnancement upload pieces jointes avant generation rapport final, logging erreurs fusion PDF, grille 2x2 photos annexees</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>4 correctifs, aucun changement de schema DB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4956,6 +4956,40 @@
         </is>
       </c>
     </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-140</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Uniformisation champ équipement signalement</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Champ Related Equipment (recherche par tag number, cross-catégorie) uniformisé sur les 4 onglets Bio/Infra/IT/Autre du formulaire de signalement d'incident</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>EquipmentPickerField conservé (encore utilisé dans issue_detail_screen.dart, contrairement à l'hypothèse initiale) ; flutter analyze OK ; /simplify appliqué (4 agents en parallèle)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4990,6 +4990,104 @@
         </is>
       </c>
     </row>
+    <row r="142" ht="28" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-141</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Upload immédiat pièces jointes intervention</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Corrige la lenteur de Save-and-Close (upload décalé à la sélection du fichier) et l'absence de documents dans l'onglet Documents (fix TypeError _parseMultipartResponse + stream reload). Ajout DELETE /api/issues/:id/documents/:doc_id avec contrôle d'auteur.</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Cas A: tamponnage synchrone dans la réponse HTTP, upload déclenché maintenant à la sélection. Cas B: bug de cast JSON (Array vs Map) + état figé de InterventionDocumentsTab — corrigé via _PendingUpload + StreamController&lt;void&gt; broadcast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-142</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Autocomplétion équipement IssueForm</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Remplace champ tag + bouton recherche par RawAutocomplete&lt;Equipment&gt; sur les 4 onglets, recherche locale nom+tags, compatible QR scan et hasUnsavedData</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-143</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Raison affichée pour échec upload pièce jointe intervention</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Le message de clôture 'Closed successfully, but some files could not be uploaded' n'affichait que les noms de fichiers sans expliquer pourquoi. Capture désormais le message d'erreur serveur (type non supporté, fichier trop volumineux, etc.) et l'affiche dans le SnackBar de clôture + tooltip sur le chip du fichier en échec.</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Fichier: technician_intervention_update_screen.dart. Le serveur renvoyait déjà un message JSON exploitable (index.js:86-98), il était juste ignoré côté client (catch (e) -&gt; debugPrint seul).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5088,6 +5088,36 @@
         </is>
       </c>
     </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-144</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Correctifs annexes intervention</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Uploader photos issue tracé (uploaded_by/uploader_name), tag_number equipement affiche dans les rapports PDF (loop/final), nom de telechargement convivial (equipement-tag-issue-annexe) pour photos/documents et export ZIP.</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5118,6 +5118,206 @@
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr"/>
     </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-145</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Instrumentation KPI des skills + /improve-skill</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Base SQLite hors repo (~/.claude/skills-data) + contexte vivant par skill + script skill_metrics.py (durée/tokens/qualité). /feature-to-prompt instrumenté (phases 0-pré et 7), nouveau skill /improve-skill (analyse KPI + amélioration SKILL.md).</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Contrat commun : .claude/skills/_shared/INSTRUMENTATION.md. Script testé (start/end/report/log-improvement, mesure tokens réelle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="28" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-146</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Boucle KPI des prompts générés (feature-prompt-exec)</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Les prompts produits par /feature-to-prompt embarquent 2 sections obligatoires : Suivi KPI de l'exécution (run feature-prompt-exec + label slug, affichage KPI fin d'implémentation) et Amélioration continue (/improve-skill mode retour d'exécution vers feature-to-prompt).</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>skill_metrics.py : colonne label (migration idempotente) + --label sur start. improve-skill : Phase R (modif SKILL.md seulement si défaut récurrent &gt;= 2 exécutions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-147</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Mémoire de recherche + matrice modèles/efforts des skills</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>feature-to-prompt : RESEARCH.md hors repo (cache comparaisons marché, ancrages code, refs) consulté avant toute recherche ; PARAMS.json hors repo (exécuteur/modèle/effort par phase, subagents haiku/opus). improve-skill : 3 leviers (SKILL.md, PARAMS.json 1 param à la fois avec corrélation params v&lt;N&gt;-KPIs, consolidation RESEARCH.md) + auto-réglage de sa propre matrice.</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Défauts versionnés : params.default.json + research.template.md dans chaque dossier de skill. Contrat mis à jour dans _shared/INSTRUMENTATION.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="28" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-148</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Benchmark web des skills + 5 améliorations</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Recherche web sur les skills comparables (claude-improve, claude-reflect, prompt-architect, sdd-brainstorm, superpowers, skill-creator Anthropic), archivée dans les RESEARCH.md hors repo. Appliqué : snapshot/rollback versions/ + confiance/décroissance des leçons (improve-skill) ; score v0 + arbre par type de feature + 2-3 options d'approche (feature-to-prompt).</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Suivi d'acceptation écarté par l'utilisateur. Pistes non retenues (éval train/test, OTel) notées dans RESEARCH.md improve-skill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="28" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-149</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Rôle supervisor consultation+rapports</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Retrait approveRequests/assignTasks, ajout generateReports, 403 backend mutations issues, ordre sidebar, rapport KPI mensuel par email (cron + Brevo + opt-out)</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Migration one-shot _supervisor_role_v2; cron 0 6 1 * *; route debug send-monthly-report; toggle opt-out Flutter; analytics ajouté au module équipement</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-150</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Auto-réparation verifyEmail realm Keycloak</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>auth-service détecte et corrige au démarrage toute dérive du réglage realm verifyEmail (doit rester false), qui bloquait le login des nouveaux comptes access-request quand le script de déploiement Jenkins échouait silencieusement (|| true)</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5318,6 +5318,36 @@
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr"/>
     </row>
+    <row r="152" ht="28" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-151</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Import CSV équipements + correctif formulaire (warranty_end_date)</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Route POST /api/equipment/import-csv (RBAC admin/supervisor/technicien*, dry-run, slug anti-collision, doublon serial_number), colonnes created_by_id/name, champ warranty_end_date ajouté au formulaire Nouvel équipement, UI Flutter (bouton+dialog+modèle CSV+rapport erreurs).</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5348,6 +5348,36 @@
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr"/>
     </row>
+    <row r="153" ht="28" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-152</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Audit et correction i18n résiduel</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Correction des chaînes françaises en dur dans écrans+widgets Flutter, rapport audit/rapport_i18n_2026-07-06.md</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5378,6 +5378,100 @@
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr"/>
     </row>
+    <row r="154" ht="28" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-153</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Script update.sh</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Mise à jour d'un déploiement IP-only déjà provisionné (backup auto + pull + restart + re-sync rôles Keycloak)</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155" ht="28" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-154</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Fix seed Keycloak non-idempotent (Jenkins)</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>keycloak-seed.js recréait les comptes démo supprimés à chaque déploiement Jenkins (prod+dev) car il ne vérifiait que l'existence par email, pas l'historique de suppression. Ajout d'un attribut realm demoSeeded, vérifié avant tout seed.</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>auth-service/scripts/keycloak-seed.js modifié. Jenkinsfile inchangé (fix contenu dans le script). npm test auth-service : 206/206 OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="28" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-155</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Analytics Équipements + KPI + export CSV enrichi</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Renommage ReportsScreen en Analytics Équipements, ajout MTBF/backlog/obsolescence/criticité ABC/downtime, 4 colonnes CSV supplémentaires</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5472,6 +5472,36 @@
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr"/>
     </row>
+    <row r="157" ht="28" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-156</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Fusion Reports+Analytics</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Ecrans ReportsScreen et AnalyticsScreen fusionnes en un seul ecran Analytics a 2 onglets (Rapports / Analytique)</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5502,6 +5502,70 @@
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr"/>
     </row>
+    <row r="158" ht="28" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-157</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Création équipement ouverte aux techniciens</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Le bouton 'Nouvel équipement' (equipment_list_screen.dart) et la route POST /api/equipment (backend) étaient réservés à admin/supervisor ; alignés sur le garde-fou déjà utilisé pour l'import CSV (_canEdit / TECH_ROLES), ouvrant la création manuelle aux 3 rôles techniciens.</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Tests RBAC mis à jour (rbac_equipment_issues.test.js, equipment_import_csv.test.js) ; npm test (396/396) et flutter analyze OK, aucune erreur bloquante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="28" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-158</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Tag physique obligatoire</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Tag obligatoire + unique a la creation/edition d'equipement (UI + API), unicite seule sur import CSV</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5566,6 +5566,74 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr"/>
     </row>
+    <row r="160" ht="28" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-159</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Raccourci Autre recherche infra</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Bouton texte avant la recherche rapide de l'onglet Infrastructure, fixe directement _infraCategory='Other'</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>UI only, aucun changement backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="28" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-160</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Fix déconnexions - race condition refresh token</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Verrou de concurrence sur ApiClient._tryRefresh (rotation stricte Keycloak), refresh proactif avant expiration, idempotence des durées de session dans keycloak-init.js</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>flutter analyze vert (0 erreur) ; npm test auth-service 206/206 vert ; flutter test bloqué par bug environnement pré-existant (hook natif objective_c casse sur espace du chemin projet, indépendant du fix) ; vérification manuelle par trace de code (stack Keycloak/Docker non démarré) ; hypothèse PUT partiel Keycloak différée (Docker indisponible)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5634,6 +5634,40 @@
         </is>
       </c>
     </row>
+    <row r="162" ht="28" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-161</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Audit UX parcours incident</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Audit multi-agents oeil neuf du parcours de signalement (5 segments, FR+EN) : rapport, correctifs ARB, prompts par page</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>50 constats (0 bloquant, 20 genants, 30 mineurs), 0 refute ; 24 couverts par ARB ; 4 prompts pages 1/3/4/5 ; passe navigateur en repli statique (Docker indisponible)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5668,6 +5668,36 @@
         </is>
       </c>
     </row>
+    <row r="163" ht="28" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-162</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Aide novice formulaire d'incident</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Bandeau d'intro, hints enrichis (tag/description), rappel SLA par urgence, aide non répertorié - IssueFormScreen, 4 onglets</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5698,6 +5698,66 @@
       <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr"/>
     </row>
+    <row r="164" ht="28" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-163</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Correction équipement lié à un incident</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /link-equipment débloqué pour corriger un équipement déjà lié (motif obligatoire), UI ajoutée sur IssueDetailScreen et TechnicianInterventionUpdateScreen</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165" ht="28" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-164</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Logs de diffusion notifications + test broadcast</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Journalisation agrégée de send-to-roles (table logs) + bouton de test multi-rôles dans la page Debug, historique persisté</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5758,6 +5758,36 @@
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr"/>
     </row>
+    <row r="166" ht="28" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-165</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Fix upload photos + UX formulaire signalement</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Correction du parsing de réponse multipart (faux échec + duplication au retry dans le cas nominal), suppression du texte SLA sous l'urgence, reset du scroll au changement d'étape</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5788,6 +5788,74 @@
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr"/>
     </row>
+    <row r="167" ht="28" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-166</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Gestion protocoles PM depuis fiche équipement</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>CRUD protocoles PM par sous-catégorie (écrans liste/formulaire), RBAC POST/PUT élargi à supervisor+techniciens, commentaire + Pass/Fail par tâche à la validation avec auto-création d'incident consolidé, historique enrichi du checklist_snapshot</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>419 tests backend + flutter analyze OK ; flutter test bloqué par limitation environnement connue (hook native asset objective_c casse sur espace du chemin, cf run #8 mémoire)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="28" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-167</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Sélecteur catalogue Fabricant/Modèle (recherche + ajout)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Dialog unifié recherche+dropdown+ajouter pour rattacher fabricant/modèle catalogue depuis la fiche détail équipement, remplace l'édition texte libre ; RBAC POST/PUT brands+models aligné sur PUT équipement</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Composant CatalogSearchField réutilisable (RawAutocomplete, zéro dépendance). Test manuel navigateur non exécuté (Docker/Keycloak non démarré dans l'environnement) — edge cases tracés contre le code à la place.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5856,6 +5856,36 @@
         </is>
       </c>
     </row>
+    <row r="169" ht="28" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-168</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostic + observabilité push iOS</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Distinction 'accepté par le service push' vs 'confirmé reçu sur l'appareil' (accusé de réception SW), bouton self-test, écran admin de diagnostic des souscriptions push.</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5886,6 +5886,40 @@
       <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr"/>
     </row>
+    <row r="170" ht="28" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-169</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Fix validation tag_number sur PUT equipment</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/equipment/:id n'exige plus tag_number sur toute edition partielle (fabricant/modele, departement, localisation...) quand l'equipement n'a pas encore de tag - seule la creation (POST) l'exige desormais, PUT valide uniquement si le champ est explicitement envoye</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Bug remonte par l'utilisateur: dialog Manufacturer/model + Save echouait avec 'Le tag physique (tag_number) est requis'. 420/420 tests db-service passent.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5920,6 +5920,36 @@
         </is>
       </c>
     </row>
+    <row r="171" ht="28" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-170</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Bouton + création fabricant/modèle</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Bouton + explicite (dialog dédié, garde anti double-clic, message 409 spécifique) à côté des champs Fabricant/Modèle du dialog d'édition catalogue sur la fiche équipement, en complément du mécanisme de création via la recherche existante</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/verification/suivi_verifications.xlsx
+++ b/verification/suivi_verifications.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5950,6 +5950,40 @@
       <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr"/>
     </row>
+    <row r="172" ht="28" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>FEAT-171</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Fix compte bloque apres promotion admin</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/users/:id renvoyait un email/username absent quand seul le role changeait (dialogue user_detail_screen sans champ email), et Keycloak effacait l'email existant -&gt; compte injoignable au login suivant. Le endpoint renvoie desormais toujours l'email courant.</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>En attente de revue</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>auth-service/src/routes/users.js:174-186. npm test OK (206/206). A verifier en reproduisant le cas sur un compte Keycloak reel.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
